--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -597,8 +597,10 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/national/estonia
-https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
+https://oecd.ai/en/dashboards/national/estonia
+https://www.kratid.ee/en/kratt-visioon</t>
         </is>
       </c>
     </row>
@@ -630,7 +632,8 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+https://oecd.ai/en/dashboards/national/estonia</t>
         </is>
       </c>
     </row>
@@ -662,7 +665,9 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-ENAISXX-2019
+https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-20-4102
+https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
         </is>
       </c>
     </row>
@@ -694,7 +699,8 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023</t>
+          <t>https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023
+https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -726,7 +732,8 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://news.err.ee/1609250613/estonia-to-invest-85m-in-boosting-ai-uptake-across-public-private-sectors</t>
+          <t>https://news.err.ee/1609250613/estonia-to-invest-85m-in-boosting-ai-uptake-across-public-private-sectors
+https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
         </is>
       </c>
     </row>
@@ -758,7 +765,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
+https://www.kratid.ee/en/kratt-visioon</t>
         </is>
       </c>
     </row>
@@ -790,7 +798,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
         </is>
       </c>
     </row>
@@ -822,7 +831,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
+          <t>https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
+https://e-estonia.com/ai-and-the-kratt-momentum/</t>
         </is>
       </c>
     </row>
@@ -854,7 +864,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
+https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -886,7 +897,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/national/estonia</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+https://oecd.ai/en/dashboards/national/estonia</t>
         </is>
       </c>
     </row>
@@ -918,7 +930,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://e-estonia.com/ai-and-the-kratt-momentum/</t>
+          <t>https://e-estonia.com/ai-and-the-kratt-momentum/
+https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
         </is>
       </c>
     </row>
@@ -950,7 +963,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
+https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -982,7 +996,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/national/estonia</t>
+          <t>https://oecd.ai/en/dashboards/national/estonia
+https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1029,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/en/publications/progress-in-implementing-the-european-union-coordinated-plan-on-artificial-intelligence-volume-1_533c355d-en/full-report.html</t>
+          <t>https://www.oecd.org/en/publications/progress-in-implementing-the-european-union-coordinated-plan-on-artificial-intelligence-volume-1_533c355d-en/full-report.html
+https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1062,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1094,8 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1122,13 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Consultas con industria/academia; debate público 'kratt law' (2017-19) anterior a la estrategia; sin resultados formales publicados.  [confianza: MEDIA · PRELIM]</t>
+          <t>Consultas con industria/academia; debate público 'kratt law' (2017-19) anterior; sin resultados formales publicados.  [confianza: MEDIA · PRELIM]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://medium.com/e-residency-blog/estonia-starts-public-discussion-legalising-ai-166cb8e34596</t>
+          <t>https://medium.com/e-residency-blog/estonia-starts-public-discussion-legalising-ai-166cb8e34596
+https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1160,8 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-10-9801</t>
+          <t>https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-10-9801
+https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1193,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs</t>
+          <t>https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
+https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1226,9 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
+https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
+https://oecd.ai/en/dashboards/national/estonia</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1260,8 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023</t>
+          <t>https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023
+https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1365,8 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/policy-initiatives/oecd-ai-principles-9705</t>
+          <t>https://oecd.ai/en/dashboards/policy-initiatives/oecd-ai-principles-9705
+https://oecd.ai/en/ai-principles</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1438,8 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://artificialintelligenceact.eu</t>
+          <t>https://eur-lex.europa.eu/eli/reg/2024/1689/oj
+https://artificialintelligenceact.eu</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1536,8 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>https://www.aki.ee/en</t>
+          <t>https://www.aki.ee/en
+https://www.dlapiperdataprotection.com/?t=authority&amp;c=EE</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1832,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>55,75 % (2024) / 59,57 % (2025) de generación renovable. Verificación determinística: 3,49/6,26 TWh = 55,75 %. ERNC ≈ renovables (hidro ~0,5 %).  [confianza: ALTA]</t>
+          <t>55,75 % (2024) / 59,57 % (2025) de generación renovable. Determinístico: 3,49/6,26 TWh = 55,75 %. ERNC ≈ renovables (hidro ~0,5 %).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -525,7 +525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Compendio exhaustivo de URLs: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
+          <t>Cada URL va etiquetada [oficial] (gobierno, BOE/Diário da República, ISO/ITU, OCDE, dato primario) o [secundaria] (prensa, despacho, agregador). Compendio exhaustivo: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Fuentes y URLs</t>
+          <t>Fuentes y URLs  ([oficial] primaria · [secundaria] corrobora)</t>
         </is>
       </c>
     </row>
@@ -597,10 +597,10 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
-https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
-https://oecd.ai/en/dashboards/national/estonia
-https://www.kratid.ee/en/kratt-visioon</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/national/estonia
+[oficial] https://www.kratid.ee/en/kratt-visioon
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -632,8 +632,8 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
-https://oecd.ai/en/dashboards/national/estonia</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/national/estonia
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -665,9 +665,9 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ENAISXX-2019
-https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-20-4102
-https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-20-4102
+[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ENAISXX-2019</t>
         </is>
       </c>
     </row>
@@ -699,8 +699,8 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023
-https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
+          <t>[secundaria] https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -732,8 +732,8 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://news.err.ee/1609250613/estonia-to-invest-85m-in-boosting-ai-uptake-across-public-private-sectors
-https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
+[secundaria] https://news.err.ee/1609250613/estonia-to-invest-85m-in-boosting-ai-uptake-across-public-private-sectors</t>
         </is>
       </c>
     </row>
@@ -765,8 +765,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
-https://www.kratid.ee/en/kratt-visioon</t>
+          <t>[oficial] https://www.kratid.ee/en/kratt-visioon
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -798,8 +798,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
-https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
+          <t>[oficial] https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -831,8 +831,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
-https://e-estonia.com/ai-and-the-kratt-momentum/</t>
+          <t>[oficial] https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
+[oficial] https://e-estonia.com/ai-and-the-kratt-momentum/</t>
         </is>
       </c>
     </row>
@@ -864,8 +864,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
-https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
+          <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -897,8 +897,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
-https://oecd.ai/en/dashboards/national/estonia</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/national/estonia
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -930,8 +930,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://e-estonia.com/ai-and-the-kratt-momentum/
-https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
+          <t>[oficial] https://e-estonia.com/ai-and-the-kratt-momentum/
+[oficial] https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
         </is>
       </c>
     </row>
@@ -963,8 +963,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
-https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
+          <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -996,8 +996,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/national/estonia
-https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/national/estonia
+[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -1029,8 +1029,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/en/publications/progress-in-implementing-the-european-union-coordinated-plan-on-artificial-intelligence-volume-1_533c355d-en/full-report.html
-https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/</t>
+          <t>[oficial] https://www.oecd.org/en/publications/progress-in-implementing-the-european-union-coordinated-plan-on-artificial-intelligence-volume-1_533c355d-en/full-report.html
+[secundaria] https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,8 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>[oficial] https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -1094,8 +1095,8 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
-https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf</t>
+          <t>[oficial] https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -1127,8 +1128,8 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://medium.com/e-residency-blog/estonia-starts-public-discussion-legalising-ai-166cb8e34596
-https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
+          <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
+[secundaria] https://medium.com/e-residency-blog/estonia-starts-public-discussion-legalising-ai-166cb8e34596</t>
         </is>
       </c>
     </row>
@@ -1160,8 +1161,8 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-10-9801
-https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-10-9801
+[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
         </is>
       </c>
     </row>
@@ -1193,8 +1194,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
-https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>[oficial] https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
+[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
         </is>
       </c>
     </row>
@@ -1226,9 +1227,9 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
-https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
-https://oecd.ai/en/dashboards/national/estonia</t>
+          <t>[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
+[oficial] https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
+[oficial] https://oecd.ai/en/dashboards/national/estonia</t>
         </is>
       </c>
     </row>
@@ -1260,8 +1261,8 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023
-https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
+[secundaria] https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023</t>
         </is>
       </c>
     </row>
@@ -1300,8 +1301,8 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/6794475.html?view=participation
-https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
+          <t>[oficial] https://www.iso.org/committee/6794475.html?view=participation
+[secundaria] https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1334,8 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/45306.html?view=participation</t>
+          <t>[oficial] https://www.iso.org/committee/45306.html?view=participation
+[secundaria] https://en.wikipedia.org/wiki/ISO/IEC_JTC_1/SC_27</t>
         </is>
       </c>
     </row>
@@ -1365,8 +1367,8 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/policy-initiatives/oecd-ai-principles-9705
-https://oecd.ai/en/ai-principles</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/policy-initiatives/oecd-ai-principles-9705
+[oficial] https://oecd.ai/en/ai-principles</t>
         </is>
       </c>
     </row>
@@ -1405,8 +1407,8 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/RAI-EE-NA-E2AIAXX-2024
-https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+          <t>[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-E2AIAXX-2024</t>
         </is>
       </c>
     </row>
@@ -1438,8 +1440,8 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/reg/2024/1689/oj
-https://artificialintelligenceact.eu</t>
+          <t>[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj
+[secundaria] https://artificialintelligenceact.eu</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1473,8 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/</t>
+          <t>[secundaria] https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/
+[secundaria] https://artificialintelligenceact.eu/ai-regulatory-sandbox-approaches-eu-member-state-overview/</t>
         </is>
       </c>
     </row>
@@ -1503,8 +1506,8 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>https://www.dlapiperdataprotection.com/?t=law&amp;c=EE
-https://www.riigiteataja.ee/en/eli/523012019001/consolide</t>
+          <t>[oficial] https://www.riigiteataja.ee/en/eli/523012019001/consolide
+[secundaria] https://www.dlapiperdataprotection.com/?t=law&amp;c=EE</t>
         </is>
       </c>
     </row>
@@ -1536,8 +1539,8 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>https://www.aki.ee/en
-https://www.dlapiperdataprotection.com/?t=authority&amp;c=EE</t>
+          <t>[oficial] https://www.aki.ee/en
+[secundaria] https://www.dlapiperdataprotection.com/?t=authority&amp;c=EE</t>
         </is>
       </c>
     </row>
@@ -1576,8 +1579,8 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1609,8 +1612,8 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1642,8 +1645,8 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1675,8 +1678,8 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1708,8 +1711,8 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1744,8 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai</t>
+          <t>[oficial] https://www.global-index.ai
+[secundaria] https://girai-report-2024-corrected-edition.tiiny.site/</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1777,8 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai</t>
+          <t>[oficial] https://www.global-index.ai
+[oficial] https://www.globalcenter.ai/</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1810,8 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>https://networkreadinessindex.org/country/estonia/</t>
+          <t>[oficial] https://networkreadinessindex.org/country/estonia/
+[oficial] https://download.networkreadinessindex.org/reports/countries/2025/estonia.pdf</t>
         </is>
       </c>
     </row>
@@ -1837,8 +1843,8 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
+[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -592,13 +592,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Estrategia de IA desde 2019; vigente el Data &amp; AI White Paper 2024-2030 + Action Plan (Kratt) 2024-26.  [confianza: ALTA]</t>
+          <t>Estrategia de datos+IA desde 2019; vigente el Valge raamat 2024-2030 + Tegevuskava 2024-26 (que 'on ühtlasi Eesti riiklik tehisintellekti strateegia', p.4). Validado en texto primario.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://oecd.ai/en/dashboards/national/estonia
-[oficial] https://www.kratid.ee/en/kratt-visioon
+          <t>[oficial] https://www.kratid.ee/en/kratt-visioon
 [secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
 [secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
@@ -682,9 +681,9 @@
           <t>Mecanismos de evaluación</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -694,12 +693,12 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Steering group MKM/MEAC + informes anuales + KPIs. Sin texto primario leído → PRELIM.  [confianza: MEDIA · PRELIM]</t>
+          <t>Sección 'Tegevuste elluviimine ja seire': juhtrühmad liderados por MKM dirigen y monitorean; metas y tulemusmõõdikud fijados en 'Eesti digiühiskond 2030'. Validado (Valge raamat p.12, 22).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>[secundaria] https://dig.watch/resource/estonias-national-artificial-intelligence-strategy-kratt-strategy-for-2022-2023
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
 [secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
@@ -727,13 +726,14 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>€85 millones asignados (2024-2026).  [confianza: ALTA]</t>
+          <t>Tegevuskava con presupuesto por periodo: 10 M€ (2019-21), 20 M€ (2022-23); €85 M anunciados para 2024-26. Validado (Tegevuskava p.4).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative
-[secundaria] https://news.err.ee/1609250613/estonia-to-invest-85m-in-boosting-ai-uptake-across-public-private-sectors</t>
+[secundaria] https://news.err.ee/1609250613/estonia-to-invest-85m-in-boosting-ai-uptake-across-public-private-sectors
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Action Plan Kratt 2024-26 con medidas e indicadores.  [confianza: ALTA]</t>
+          <t>Tegevuskava (Kratt) 2024-26 con tegevused por área (avalik sektor, erasektor, T&amp;A, keeletehnoloogia, õigusruum, HPC). Validado en el Plan de Acción.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>NO se halló un componente de género con plan de acción → 0.  [confianza: MEDIA · NO ENCONTRADO]</t>
+          <t>Género aparece SOLO como métrica (desagregación por sexo de competencias digitales): Valge raamat p.30 'soolist võrdsust mõõdetakse naiste ja meeste osakaaluna...'. No es eje con plan de acción → 0.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1078,9 +1078,9 @@
           <t>Tópico: Sostenibilidad</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>1 (BAJA)</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1090,13 +1090,13 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Mención de 'sustainability tool'; eje ambiental marginal → puntaje BAJA.  [confianza: BAJA · PRELIM]</t>
+          <t>Sostenibilidad AMBIENTAL no es arengusuund ni área de acción: 'kestlik areng' (p.6/26) = desarrollo sostenible de la economía de datos; 'rohepööre' aparece 1 vez (p.17). → 0. (Si ILIA toma 'Sostenibilidad' en sentido amplio, sería 1: decisión del operador.)  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://e-estonia.com/wp-content/uploads/factsheet-ai-strategy.pdf
-[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -1111,9 +1111,9 @@
           <t>Particip. ciudadana elaboración</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>2 (PRELIM)</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1123,13 +1123,13 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Consultas con industria/academia; debate público 'kratt law' (2017-19) anterior; sin resultados formales publicados.  [confianza: MEDIA · PRELIM]</t>
+          <t>'Kaasatud osapooled' (Valge raamat p.12): elaboración con ministerios, ITL, universidades, empresas, consorcios y parques científicos — stakeholders organizados, NO una consulta ciudadana abierta con resultados publicados → 2.  [confianza: MEDIA-ALTA]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
-[secundaria] https://medium.com/e-residency-blog/estonia-starts-public-discussion-legalising-ai-166cb8e34596</t>
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -1144,9 +1144,9 @@
           <t>Multistakeholder elaboración</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1156,13 +1156,13 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Elaboración: Gobierno + academia + industria (Gob+2).  [confianza: MEDIA · PRELIM]</t>
+          <t>Multistakeholder en la elaboración = Gob + sector privado (ITL, eraettevõtted, consorcios, teaduspargid) + academia (ülikoolid) + sociedad civil (vabaühendused). Valge raamat p.8/12 → Gob+3.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://oecd.ai/en/dashboards/policy-initiatives/national-ai-strategy-10-9801
-[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf</t>
+          <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -1177,9 +1177,9 @@
           <t>Multistakeholder implementación</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>4 (PRELIM)</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Implementación: Gobierno + academia + industria + sociedad civil (Gob+3).  [confianza: MEDIA · PRELIM]</t>
+          <t>Implementación vía juhtrühmad (MKM + asutused + 'avaliku sektori välised võtmepartnerid', p.12); áreas del AP: público, privado, academia → Gob+3.  [confianza: MEDIA-ALTA]</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://www.valitsus.ee/en/news/government-launched-eestiai-initiative-together-leading-entrepreneurs
-[oficial] https://www.riigikantselei.ee/en/supporting-government-and-prime-minister/eestiai-initiative</t>
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -1402,13 +1402,14 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>EU AI Act (Reg. UE 2024/1689) aplicable; Estonia descartó una 'kratt law' nacional propia.  [confianza: ALTA]</t>
+          <t>EU AI Act (Reg. UE 2024/1689); el Tegevuskava 2024-26 'on ühtlasi Eesti riiklik tehisintellekti strateegia EL kooskõlastatud tegevuskava mõistes' (p.4). Sin ley nacional propia de IA.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj
-[secundaria] https://regulations.ai/regulations/RAI-EE-NA-E2AIAXX-2024</t>
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-E2AIAXX-2024
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -1435,13 +1436,13 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>EU AI Act = enfoque por riesgo (prohibido/alto/limitado/mínimo).  [confianza: ALTA]</t>
+          <t>EU AI Act = enfoque por riesgo; el Valge raamat prevé 'Algoritmi mõjuhinnangu mudel' (evaluación de impacto algorítmico) (p.52). → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
           <t>[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj
-[secundaria] https://artificialintelligenceact.eu</t>
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1469,13 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Sandbox EE-FI (exigido por el EU AI Act); el gobierno ya usa sandboxes.  [confianza: ALTA]</t>
+          <t>Estonia incluye un SANDBOX nacional de IA/datos en su estrategia: 'Tehisintellekti liivakasti pakkumine era- ja avaliku sektori asutustele' (Valge raamat p.52); + sandbox transfronterizo EE-FI. → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>[secundaria] https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+[secundaria] https://www.fairedih.fi/en/2026/05/20/finland-and-estonia-bet-on-ai-sandboxes-as-europes-small-states-seek-influence-over-digital-rules/
 [secundaria] https://artificialintelligenceact.eu/ai-regulatory-sandbox-approaches-eu-member-state-overview/</t>
         </is>
       </c>

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1090,13 +1090,13 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Sostenibilidad AMBIENTAL no es arengusuund ni área de acción: 'kestlik areng' (p.6/26) = desarrollo sostenible de la economía de datos; 'rohepööre' aparece 1 vez (p.17). → 0. (Si ILIA toma 'Sostenibilidad' en sentido amplio, sería 1: decisión del operador.)  [confianza: ALTA]</t>
+          <t>Sostenibilidad/medioambiente SÍ se aborda con acciones: IA verde/eficiente 'energiasäästliku ehk «rohelise» TI arendamine' (Tegevuskava p.16-17); IA del sector público alineada con 'säästva arengu eesmärgid' (ODS, Valge raamat p.43); 'kestlikkuse tööriist' (herramienta de sostenibilidad, p.38); soluciones para 'kestlikkusele energeetikas, ehituses ja transpordis' (AP p.17); datos selectivos por 'globaalse rohejalajälje vähendamine' (p.13). → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
-[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Género aparece SOLO como métrica (desagregación por sexo de competencias digitales): Valge raamat p.30 'soolist võrdsust mõõdetakse naiste ja meeste osakaaluna...'. No es eje con plan de acción → 0.  [confianza: ALTA]</t>
+          <t>Género NO es eje con plan → 0. Búsqueda exhaustiva: solo 5 menciones en ambos PDF — la métrica de igualdad (Valge raamat p.30 'soolist võrdsust mõõdetakse naiste ja meeste osakaaluna...') y 'diskrimineerimine' genérica (riesgo p.20; proyecto de discriminación algorítmica EE-LT p.55, no específico de género). Sin proyecto/cuota/presupuesto/campaña de género; la inclusión se estructura por accesibilidad/erivajadused y territorio.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>'Kaasatud osapooled' (Valge raamat p.12): elaboración con ministerios, ITL, universidades, empresas, consorcios y parques científicos — stakeholders organizados, NO una consulta ciudadana abierta con resultados publicados → 2.  [confianza: MEDIA-ALTA]</t>
+          <t>Mecanismo de participación ciudadana con resultados publicados: en la elaboración se hicieron 'kaks omnibussi uuringut, milles osales kokku 2150 Eesti elanikku' (2 encuestas ómnibus, 2150 residentes: actitudes/expectativas/temores) + 'kaasamisintervjuusid, milles osales 220' especialistas (Tegevuskava p.6); resultado publicado p.ej. '77% Eesti elanikest suhtub pigem positiivselt' (Valge raamat p.44). → 4 (defendible 5: &gt;1 mecanismo).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024
 [secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
         </is>
       </c>

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Mecanismo de participación ciudadana con resultados publicados: en la elaboración se hicieron 'kaks omnibussi uuringut, milles osales kokku 2150 Eesti elanikku' (2 encuestas ómnibus, 2150 residentes: actitudes/expectativas/temores) + 'kaasamisintervjuusid, milles osales 220' especialistas (Tegevuskava p.6); resultado publicado p.ej. '77% Eesti elanikest suhtub pigem positiivselt' (Valge raamat p.44). → 4 (defendible 5: &gt;1 mecanismo).  [confianza: ALTA]</t>
+          <t>&gt;1 mecanismo de participación en la elaboración, con resultados publicados: 'kaks omnibussi uuringut, milles osales kokku 2150 Eesti elanikku' (2 encuestas ómnibus, 2150 residentes) + 'kaasamisintervjuusid, milles osales 220' (220 entrevistas) (Tegevuskava p.6); resultado p.ej. '77% Eesti elanikest suhtub pigem positiivselt' (Valge raamat p.44). 119 mide MECANISMOS (≥2 → 5); el nº de sectores va en 121.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -1156,13 +1156,13 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Multistakeholder en la elaboración = Gob + sector privado (ITL, eraettevõtted, consorcios, teaduspargid) + academia (ülikoolid) + sociedad civil (vabaühendused). Valge raamat p.8/12 → Gob+3.  [confianza: ALTA]</t>
+          <t>Sectores en la ELABORACIÓN (VR p.8/12, PA p.6): GOBIERNO (MKM líder + Justiitsmin., HTM, Riigikantselei, todos los ministerios y agencias) + PRIVADO (eraettevõtted, asociación ITL, consorcios de empresas, teaduspargid) + ACADEMIA (ülikoolid, instituciones de educación/investigación, Eesti Keele Instituut) + SOCIEDAD CIVIL (vabaühendused). → Gob+3 = 4.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://knowledge4policy.ec.europa.eu/sites/default/files/estonia-ai-strategy-report.pdf
-[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024</t>
+          <t>[secundaria] https://regulations.ai/regulations/RAI-EE-NA-DAIWPXX-2024
+[secundaria] https://regulations.ai/regulations/RAI-EE-NA-ADAPKXX-2024</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Implementación vía juhtrühmad (MKM + asutused + 'avaliku sektori välised võtmepartnerid', p.12); áreas del AP: público, privado, academia → Gob+3.  [confianza: MEDIA-ALTA]</t>
+          <t>Sectores en la IMPLEMENTACIÓN (VR p.12/33): GOBIERNO (juhtrühmad liderados por MKM + ministerios + RIA + Statistikaamet + gobiernos locales + centros de competencia) + PRIVADO (erasektor; empresas vía AIRE) + ACADEMIA (universidades asociadas vía AIRE; Eesti Keele Instituut); las juhtrühmad suman 'avaliku sektori välised võtmepartnerid' y rinden cuentas al público vía 'andmete võrgustiku avatud kohtumine'. → Gob+3 = 4 (estricto por sectores nombrados privado+academia: Gob+2 = 3).  [confianza: MEDIA-ALTA]</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Sectores en la ELABORACIÓN (VR p.8/12, PA p.6): GOBIERNO (MKM líder + Justiitsmin., HTM, Riigikantselei, todos los ministerios y agencias) + PRIVADO (eraettevõtted, asociación ITL, consorcios de empresas, teaduspargid) + ACADEMIA (ülikoolid, instituciones de educación/investigación, Eesti Keele Instituut) + SOCIEDAD CIVIL (vabaühendused). → Gob+3 = 4.  [confianza: ALTA]</t>
+          <t>Sectores en la ELABORACIÓN (VR p.8/12, PA p.6): GOBIERNO + PRIVADO (eraettevõtted, ITL, consorcios, teaduspargid) + ACADEMIA (ülikoolid, Eesti Keele Instituut) + ONG/sin fines de lucro (vabaühendused, p.8) + PÚBLICO GENERAL (2150 residentes en 2 encuestas ómnibus + 220 entrevistas, PA p.6; el VR incorpora 'kodaniku perspektiive', p.8). Contando ONG y público como sectores distintos → Gob+4 = 5. (Si el 4º sector ILIA = organismos internacionales, sería 4: ninguno co-creó el documento.)  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">

--- a/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_EE_Estonia_ILIA2026.xlsx
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1840,13 +1840,13 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>55,75 % (2024) / 59,57 % (2025) de generación renovable. Determinístico: 3,49/6,26 TWh = 55,75 %. ERNC ≈ renovables (hidro ~0,5 %).  [confianza: ALTA]</t>
+          <t>Energía limpia 2025 = 60,26 % (renovables 60,26 % + nuclear 0; incl. hidro 0,48 %). EMBER, determinístico (renov 3,73/6,19 TWh). A confirmar con CENIA.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://ember-energy.org/data/electricity-data-explorer/
+[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv</t>
         </is>
       </c>
     </row>
